--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260611.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260611.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>159,735</t>
+          <t>162,925</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.79%</t>
+          <t>27.32%</t>
         </is>
       </c>
     </row>
@@ -633,100 +633,100 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>115,730</t>
+          <t>118,130</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.49%</t>
+          <t>9.46%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>18,215</t>
+          <t>60,105</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>7.34%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>58,955</t>
+          <t>18,575</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.71%</t>
+          <t>7.33%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>NEE US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>140,395</t>
+          <t>426,200,048</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.86%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>NEE US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>341,643,208</t>
+          <t>143,395</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.86%</t>
+          <t>5.29%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>68,830</t>
+          <t>70,230</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>75,565</t>
+          <t>77,365</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>6,635</t>
+          <t>6,765</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>52,255</t>
+          <t>53,355</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -831,56 +831,56 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>22,835</t>
+          <t>23,335</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>36,450</t>
+          <t>21,583</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>21,163</t>
+          <t>37,250</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>23,485</t>
+          <t>23,955</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>89,115</t>
+          <t>90,915</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -941,56 +941,56 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>59,125</t>
+          <t>60,305</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>30,778</t>
+          <t>9,440</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>31,398</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1007,56 +1007,56 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>22,590</t>
+          <t>23,040</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>68,658</t>
+          <t>42,800</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>9,240</t>
+          <t>70,208</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1073,56 +1073,56 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>13,561</t>
+          <t>13,831</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>24,728</t>
+          <t>11,376</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>11,116</t>
+          <t>25,228</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>146,895</t>
+          <t>149,895</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,415</t>
+          <t>21,865</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>22,847</t>
+          <t>23,307</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,491</t>
+          <t>18,871</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>43,440</t>
+          <t>44,340</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>50,070</t>
+          <t>51,070</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>13,765</t>
+          <t>14,015</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,390,199</t>
+          <t>1,372,664</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>-24,157</t>
+          <t>-69,067</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
